--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -19738,6 +19738,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B843" t="n">
+        <v>180179</v>
+      </c>
+      <c r="C843" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="E843" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G843" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -19761,6 +19761,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="844">
+      <c r="A844" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B844" t="n">
+        <v>80531</v>
+      </c>
+      <c r="C844" t="n">
+        <v>2</v>
+      </c>
+      <c r="D844" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="E844" t="n">
+        <v>2</v>
+      </c>
+      <c r="F844" t="n">
+        <v>1.9650000333786</v>
+      </c>
+      <c r="G844" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -19784,6 +19784,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="845">
+      <c r="A845" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B845" t="n">
+        <v>165255</v>
+      </c>
+      <c r="C845" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="D845" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="E845" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="F845" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G845" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -19807,6 +19807,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B846" t="n">
+        <v>127310</v>
+      </c>
+      <c r="C846" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D846" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E846" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F846" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G846" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -19648,22 +19648,22 @@
     </row>
     <row r="839">
       <c r="A839" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B839" t="n">
-        <v>308964</v>
+        <v>73045</v>
       </c>
       <c r="C839" t="n">
-        <v>2.10999989509583</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="D839" t="n">
-        <v>2.01999998092651</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="E839" t="n">
-        <v>2.09999990463257</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="F839" t="n">
-        <v>2.05999994277954</v>
+        <v>2.07999992370605</v>
       </c>
       <c r="G839" t="s">
         <v>7</v>
@@ -19671,22 +19671,22 @@
     </row>
     <row r="840">
       <c r="A840" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B840" t="n">
-        <v>330195</v>
+        <v>308964</v>
       </c>
       <c r="C840" t="n">
-        <v>2.16000008583069</v>
+        <v>2.10999989509583</v>
       </c>
       <c r="D840" t="n">
         <v>2.01999998092651</v>
       </c>
       <c r="E840" t="n">
-        <v>2.04999995231628</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="F840" t="n">
-        <v>2.11999988555908</v>
+        <v>2.05999994277954</v>
       </c>
       <c r="G840" t="s">
         <v>7</v>
@@ -19694,22 +19694,22 @@
     </row>
     <row r="841">
       <c r="A841" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B841" t="n">
-        <v>384852</v>
+        <v>330195</v>
       </c>
       <c r="C841" t="n">
-        <v>2.14000010490417</v>
+        <v>2.16000008583069</v>
       </c>
       <c r="D841" t="n">
-        <v>1.92999994754791</v>
+        <v>2.01999998092651</v>
       </c>
       <c r="E841" t="n">
-        <v>2.14000010490417</v>
+        <v>2.04999995231628</v>
       </c>
       <c r="F841" t="n">
-        <v>1.9650000333786</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="G841" t="s">
         <v>7</v>
@@ -19717,22 +19717,22 @@
     </row>
     <row r="842">
       <c r="A842" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B842" t="n">
-        <v>244281</v>
+        <v>384852</v>
       </c>
       <c r="C842" t="n">
-        <v>1.99000000953674</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="D842" t="n">
-        <v>1.875</v>
+        <v>1.92999994754791</v>
       </c>
       <c r="E842" t="n">
-        <v>1.99000000953674</v>
+        <v>2.14000010490417</v>
       </c>
       <c r="F842" t="n">
-        <v>1.91499996185303</v>
+        <v>1.9650000333786</v>
       </c>
       <c r="G842" t="s">
         <v>7</v>
@@ -19740,22 +19740,22 @@
     </row>
     <row r="843">
       <c r="A843" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B843" t="n">
-        <v>180179</v>
+        <v>244281</v>
       </c>
       <c r="C843" t="n">
-        <v>1.98000001907349</v>
+        <v>1.99000000953674</v>
       </c>
       <c r="D843" t="n">
-        <v>1.87000000476837</v>
+        <v>1.875</v>
       </c>
       <c r="E843" t="n">
-        <v>1.88499999046326</v>
+        <v>1.99000000953674</v>
       </c>
       <c r="F843" t="n">
-        <v>1.96000003814697</v>
+        <v>1.91499996185303</v>
       </c>
       <c r="G843" t="s">
         <v>7</v>
@@ -19763,22 +19763,22 @@
     </row>
     <row r="844">
       <c r="A844" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B844" t="n">
-        <v>80531</v>
+        <v>180179</v>
       </c>
       <c r="C844" t="n">
-        <v>2</v>
+        <v>1.98000001907349</v>
       </c>
       <c r="D844" t="n">
-        <v>1.93499994277954</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="E844" t="n">
-        <v>2</v>
+        <v>1.88499999046326</v>
       </c>
       <c r="F844" t="n">
-        <v>1.9650000333786</v>
+        <v>1.96000003814697</v>
       </c>
       <c r="G844" t="s">
         <v>7</v>
@@ -19786,22 +19786,22 @@
     </row>
     <row r="845">
       <c r="A845" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B845" t="n">
-        <v>165255</v>
+        <v>80531</v>
       </c>
       <c r="C845" t="n">
-        <v>2.08999991416931</v>
+        <v>2</v>
       </c>
       <c r="D845" t="n">
-        <v>1.97500002384186</v>
+        <v>1.93499994277954</v>
       </c>
       <c r="E845" t="n">
-        <v>1.99000000953674</v>
+        <v>2</v>
       </c>
       <c r="F845" t="n">
-        <v>2.04999995231628</v>
+        <v>1.9650000333786</v>
       </c>
       <c r="G845" t="s">
         <v>7</v>
@@ -19809,24 +19809,47 @@
     </row>
     <row r="846">
       <c r="A846" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B846" t="n">
-        <v>127310</v>
+        <v>165255</v>
       </c>
       <c r="C846" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="D846" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="E846" t="n">
+        <v>1.99000000953674</v>
+      </c>
+      <c r="F846" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G846" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B847" t="n">
+        <v>137667</v>
+      </c>
+      <c r="C847" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="D847" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="E847" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F847" t="n">
         <v>2.14000010490417</v>
       </c>
-      <c r="D846" t="n">
-        <v>2.01999998092651</v>
-      </c>
-      <c r="E846" t="n">
-        <v>2.01999998092651</v>
-      </c>
-      <c r="F846" t="n">
-        <v>2.11999988555908</v>
-      </c>
-      <c r="G846" t="s">
+      <c r="G847" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22449,6 +22449,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B850" t="n">
+        <v>40952</v>
+      </c>
+      <c r="C850" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E850" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="G850" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="H850" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22475,6 +22475,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="851">
+      <c r="A851" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B851" t="n">
+        <v>28684</v>
+      </c>
+      <c r="C851" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="D851" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E851" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F851" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G851" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="H851" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22501,6 +22501,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="852">
+      <c r="A852" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B852" t="n">
+        <v>75440</v>
+      </c>
+      <c r="C852" t="n">
+        <v>2.17000007629395</v>
+      </c>
+      <c r="D852" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="E852" t="n">
+        <v>2.17000007629395</v>
+      </c>
+      <c r="F852" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="G852" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="H852" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22527,6 +22527,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B853" t="n">
+        <v>43121</v>
+      </c>
+      <c r="C853" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="D853" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E853" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="F853" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G853" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H853" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22605,6 +22605,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B856" t="n">
+        <v>19676</v>
+      </c>
+      <c r="C856" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D856" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E856" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F856" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G856" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H856" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -20122,8 +20122,31 @@
       <c r="E859" t="n">
         <v>2.0699999332428</v>
       </c>
-      <c r="F859"/>
+      <c r="F859" t="n">
+        <v>2.1800000667572</v>
+      </c>
       <c r="G859" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B860" t="n">
+        <v>129293</v>
+      </c>
+      <c r="C860" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D860" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="E860" t="n">
+        <v>2.17000007629395</v>
+      </c>
+      <c r="F860"/>
+      <c r="G860" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -20145,8 +20145,31 @@
       <c r="E860" t="n">
         <v>2.17000007629395</v>
       </c>
-      <c r="F860"/>
+      <c r="F860" t="n">
+        <v>2.19000005722046</v>
+      </c>
       <c r="G860" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B861" t="n">
+        <v>47661</v>
+      </c>
+      <c r="C861" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D861" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="E861" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F861"/>
+      <c r="G861" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -20168,8 +20168,31 @@
       <c r="E861" t="n">
         <v>2.24000000953674</v>
       </c>
-      <c r="F861"/>
+      <c r="F861" t="n">
+        <v>2.16000008583069</v>
+      </c>
       <c r="G861" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B862" t="n">
+        <v>190877</v>
+      </c>
+      <c r="C862" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D862" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="E862" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="F862"/>
+      <c r="G862" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -20191,8 +20191,31 @@
       <c r="E862" t="n">
         <v>2.13000011444092</v>
       </c>
-      <c r="F862"/>
+      <c r="F862" t="n">
+        <v>2.13000011444092</v>
+      </c>
       <c r="G862" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B863" t="n">
+        <v>29970</v>
+      </c>
+      <c r="C863" t="n">
+        <v>2.17000007629395</v>
+      </c>
+      <c r="D863" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="E863" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="F863"/>
+      <c r="G863" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -20221,6 +20221,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B864" t="n">
+        <v>7895</v>
+      </c>
+      <c r="C864" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="D864" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E864" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F864" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="G864" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22891,6 +22891,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="867">
+      <c r="A867" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B867" t="n">
+        <v>56098</v>
+      </c>
+      <c r="C867" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="D867" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="E867" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F867" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G867" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="H867" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -22917,6 +22917,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="868">
+      <c r="A868" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B868" t="n">
+        <v>13489</v>
+      </c>
+      <c r="C868" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D868" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E868" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F868" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G868" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="H868" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25579,6 +25579,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="870">
+      <c r="A870" t="s">
+        <v>9</v>
+      </c>
+      <c r="B870" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C870" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="D870" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E870" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="F870" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="G870" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="H870" t="n">
+        <v>20284</v>
+      </c>
+      <c r="I870" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25590,7 +25590,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="D870" t="n">
-        <v>2.05999994277954</v>
+        <v>2.0699999332428</v>
       </c>
       <c r="E870" t="n">
         <v>2.00999999046326</v>
@@ -25605,6 +25605,35 @@
         <v>20284</v>
       </c>
       <c r="I870" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="s">
+        <v>9</v>
+      </c>
+      <c r="B871" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C871" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="D871" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E871" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="F871" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G871" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H871" t="n">
+        <v>56900</v>
+      </c>
+      <c r="I871" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25637,6 +25637,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="872">
+      <c r="A872" t="s">
+        <v>9</v>
+      </c>
+      <c r="B872" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C872" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="D872" t="n">
+        <v>2.13000011444092</v>
+      </c>
+      <c r="E872" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="F872" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G872" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="H872" t="n">
+        <v>11870</v>
+      </c>
+      <c r="I872" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25666,6 +25666,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="873">
+      <c r="A873" t="s">
+        <v>9</v>
+      </c>
+      <c r="B873" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C873" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="D873" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="E873" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F873" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="G873" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="H873" t="n">
+        <v>17988</v>
+      </c>
+      <c r="I873" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25680,7 +25680,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="E873" t="n">
-        <v>2.02999997138977</v>
+        <v>2.01999998092651</v>
       </c>
       <c r="F873" t="n">
         <v>2.01999998092651</v>
@@ -25692,6 +25692,35 @@
         <v>17988</v>
       </c>
       <c r="I873" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="s">
+        <v>9</v>
+      </c>
+      <c r="B874" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C874" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D874" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="E874" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F874" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G874" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="H874" t="n">
+        <v>16087</v>
+      </c>
+      <c r="I874" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25724,6 +25724,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="875">
+      <c r="A875" t="s">
+        <v>9</v>
+      </c>
+      <c r="B875" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C875" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D875" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E875" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F875" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G875" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="H875" t="n">
+        <v>39741</v>
+      </c>
+      <c r="I875" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25753,6 +25753,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="876">
+      <c r="A876" t="s">
+        <v>9</v>
+      </c>
+      <c r="B876" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C876" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="D876" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E876" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F876" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="G876" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="H876" t="n">
+        <v>44015</v>
+      </c>
+      <c r="I876" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25782,6 +25782,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="877">
+      <c r="A877" t="s">
+        <v>9</v>
+      </c>
+      <c r="B877" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C877" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D877" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E877" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F877" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G877" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="H877" t="n">
+        <v>42758</v>
+      </c>
+      <c r="I877" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DEX.MI.xlsx
+++ b/data/DEX.MI.xlsx
@@ -25811,6 +25811,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="878">
+      <c r="A878" t="s">
+        <v>9</v>
+      </c>
+      <c r="B878" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C878" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D878" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="E878" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F878" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="G878" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="H878" t="n">
+        <v>18343</v>
+      </c>
+      <c r="I878" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
